--- a/public/data/cc_info.xlsx
+++ b/public/data/cc_info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pires\pires-lab.github.io\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721F2344-AC3D-4F4E-BF99-5D8A0A063495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B346D40B-9533-45C9-B17E-821934FBAE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{318A5430-794F-40FC-A173-304C21893E06}"/>
   </bookViews>
